--- a/stories/arbres/ATOM-JEU.BAS.001-06.xlsx
+++ b/stories/arbres/ATOM-JEU.BAS.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Blaise et papa sont au gymnase. Un petit panier est accroché bas. Papa donne le ballon. Papa dit : on va passer le ballon. Ensuite, chacun a un lancer. Blaise passe. Papa rend. C'est le lancer de Blaise. Il lance vers le panier. Le ballon rentre. Papa a son lancer. Blaise dit : chacun un lancer. Ils se passent encore le ballon.</t>
+          <t>Blaise et papa sont au gymnase. Un petit panier est accroché bas. Papa donne le ballon. On va passer le ballon. Ensuite, chacun a un lancer. Blaise passe. Papa rend. C'est le lancer de Blaise. Il lance vers le panier. Le ballon rentre. Papa a son lancer. Chacun un lancer. Ils se passent encore le ballon.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Blaise et papa sont au gymnase. Un petit panier est accroché bas. Papa donne le ballon.
+papa|On va passer le ballon. Ensuite, chacun a un lancer.
+narrateur|Blaise passe. Papa rend. C'est le lancer de Blaise. Il lance vers le panier. Le ballon rentre. Papa a son lancer.
+enfant-f|Chacun un lancer.
+narrateur|Ils se passent encore le ballon.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Blaise joue au basket. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Blaise a passé le ballon. Il a visé le panier. Chacun a eu un lancer.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range le ballon. Blaise essuie ses mains.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAS.001-06.xlsx
+++ b/stories/arbres/ATOM-JEU.BAS.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Ils se passent encore le ballon.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Blaise joue au basket. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Blaise a passé le ballon. Il a visé le panier. Chacun a eu un lancer.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Papa range le ballon. Blaise essuie ses mains.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.BAS.001-06.xlsx
+++ b/stories/arbres/ATOM-JEU.BAS.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Blaise vise le panier au gymnase</t>
+          <t>La gourde bleue du gymnase</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>JEU.BAL.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une gourde bleue roule sur le bois du gymnase. Amir se passe le ballon avec papa. Chacun a un lancer vers le petit panier.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Blaise et papa sont au gymnase. Un petit panier est accroché bas. Papa donne le ballon. On va passer le ballon. Ensuite, chacun a un lancer. Blaise passe. Papa rend. C'est le lancer de Blaise. Il lance vers le panier. Le ballon rentre. Papa a son lancer. Chacun un lancer. Ils se passent encore le ballon.</t>
+          <t>Une gourde bleue roule toute seule. Elle fait un petit cercle. Le bois du gymnase est lisse. Ça sent le bois propre. Les chaussures d'Amir font toc. Toc. Toc. Tu entends l'écho, Amir ? Oui, papa. Ça répète. Une ligne jaune va tout droit. Elle brille un peu. Amir pose un doigt dessus. Elle est froide. C'est la ligne du gymnase. Le banc est vide. Un pull gris y dort. Papa pose le sac. La gourde s'arrête contre sa chaussure. Bravo. Tu l'as vue. En ce moment, Amir est au gymnase. Un petit panier est accroché bas. Le filet est blanc. Il bouge un peu. Le ballon orange est dans le sac. Papa le sort. Il rebondit une fois. Pon. On va passer le ballon. Ensuite, chacun a un lancer. Amir touche le ballon. Il est un peu grainé. Il est chaud, papa. Un peu, oui. Tu me le passes ? Amir passe le ballon. Papa le prend. Bravo. Tu as passé. Papa rend le ballon. C'est ton lancer, Amir. Amir regarde le panier. Il lance vers le panier. Le ballon touche le bord. Il rentre. Le filet fait chh. Il est dedans ! Bravo, Amir. Tu as visé le panier. Chacun a un lancer. Maintenant, c'est le mien. Papa lance. Le ballon rentre. Chacun un lancer. Oui. On se passe encore. Amir passe. Papa passe. Le bois fait un bruit doux. Amir attend. C'est encore son lancer. Il lance vers le panier. Le ballon rentre. Bravo. Tu as passé. Tu as visé. Chacun a eu un lancer.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1329,81 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Blaise et papa sont au gymnase. Un petit panier est accroché bas. Papa donne le ballon.
-papa|On va passer le ballon. Ensuite, chacun a un lancer.
-narrateur|Blaise passe. Papa rend. C'est le lancer de Blaise. Il lance vers le panier. Le ballon rentre. Papa a son lancer.
-enfant-f|Chacun un lancer.
-narrateur|Ils se passent encore le ballon.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une gourde bleue roule toute seule.
+narrateur|Elle fait un petit cercle.
+narrateur|Le bois du gymnase est lisse.
+narrateur|Ça sent le bois propre.
+narrateur|Les chaussures d'Amir font toc.
+narrateur|Toc.
+narrateur|Toc.
+papa|Tu entends l'écho, Amir ?
+enfant-m|Oui, papa.
+enfant-m|Ça répète.
+narrateur|Une ligne jaune va tout droit.
+narrateur|Elle brille un peu.
+narrateur|Amir pose un doigt dessus.
+enfant-m|Elle est froide.
+papa|C'est la ligne du gymnase.
+narrateur|Le banc est vide.
+narrateur|Un pull gris y dort.
+narrateur|Papa pose le sac.
+narrateur|La gourde s'arrête contre sa chaussure.
+papa|Bravo.
+papa|Tu l'as vue.
+narrateur|En ce moment, Amir est au gymnase.
+narrateur|Un petit panier est accroché bas.
+narrateur|Le filet est blanc.
+narrateur|Il bouge un peu.
+narrateur|Le ballon orange est dans le sac.
+narrateur|Papa le sort.
+narrateur|Il rebondit une fois.
+narrateur|Pon.
+papa|On va passer le ballon.
+papa|Ensuite, chacun a un lancer.
+narrateur|Amir touche le ballon.
+narrateur|Il est un peu grainé.
+enfant-m|Il est chaud, papa.
+papa|Un peu, oui.
+papa|Tu me le passes ?
+narrateur|Amir passe le ballon.
+narrateur|Papa le prend.
+papa|Bravo.
+papa|Tu as passé.
+narrateur|Papa rend le ballon.
+papa|C'est ton lancer, Amir.
+narrateur|Amir regarde le panier.
+narrateur|Il lance vers le panier.
+narrateur|Le ballon touche le bord.
+narrateur|Il rentre.
+narrateur|Le filet fait chh.
+enfant-m|Il est dedans !
+papa|Bravo, Amir.
+papa|Tu as visé le panier.
+papa|Chacun a un lancer.
+papa|Maintenant, c'est le mien.
+narrateur|Papa lance.
+narrateur|Le ballon rentre.
+enfant-m|Chacun un lancer.
+papa|Oui.
+papa|On se passe encore.
+narrateur|Amir passe.
+narrateur|Papa passe.
+narrateur|Le bois fait un bruit doux.
+narrateur|Amir attend.
+narrateur|C'est encore son lancer.
+narrateur|Il lance vers le panier.
+narrateur|Le ballon rentre.
+papa|Bravo.
+papa|Tu as passé.
+papa|Tu as visé.
+papa|Chacun a eu un lancer.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>ballon,pas</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1428,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Blaise joue au basket. Que fait-il ?</t>
+          <t>Amir joue au basket. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1584,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Blaise joue au basket. Que fait-il ?</t>
+          <t>narrateur|Amir joue au basket.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1613,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Blaise a passé le ballon. Il a visé le panier. Chacun a eu un lancer.</t>
+          <t>Amir a passé le ballon. Il a visé le panier. Chacun a eu un lancer. Tu as passé, Amir. Bravo. Tu as visé le panier. Chacun un lancer.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,7 +1757,13 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Blaise a passé le ballon. Il a visé le panier. Chacun a eu un lancer.</t>
+          <t>narrateur|Amir a passé le ballon.
+narrateur|Il a visé le panier.
+narrateur|Chacun a eu un lancer.
+papa|Tu as passé, Amir.
+papa|Bravo.
+papa|Tu as visé le panier.
+enfant-m|Chacun un lancer.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1700,7 +1791,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range le ballon. Blaise essuie ses mains.</t>
+          <t>Papa range le ballon dans le sac. Amir essuie ses mains. Elles sont un peu chaudes. La gourde bleue est là. Tu bois une gorgée ? Oui, papa. L'eau est fraîche. On a visé le panier. Oui. On s'est passé le ballon. Chacun a eu un lancer. Bravo. Tu as fait du bon travail. Le pull gris est encore sur le banc. Amir le prend. Il sent le bois. Oui. Un peu. Merci. Leurs chaussures font toc dans le couloir. On rentre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,10 +1931,34 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range le ballon. Blaise essuie ses mains.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Papa range le ballon dans le sac.
+narrateur|Amir essuie ses mains.
+narrateur|Elles sont un peu chaudes.
+narrateur|La gourde bleue est là.
+papa|Tu bois une gorgée ?
+enfant-m|Oui, papa.
+enfant-m|L'eau est fraîche.
+papa|On a visé le panier.
+enfant-m|Oui.
+enfant-m|On s'est passé le ballon.
+papa|Chacun a eu un lancer.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le pull gris est encore sur le banc.
+narrateur|Amir le prend.
+enfant-m|Il sent le bois.
+papa|Oui.
+papa|Un peu.
+papa|Merci.
+narrateur|Leurs chaussures font toc dans le couloir.
+papa|On rentre.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>pas</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,7 +1983,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La gourde bleue rentre dans le sac. J'ai passé. J'ai visé le panier. Bravo, Amir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2123,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La gourde bleue rentre dans le sac.
+enfant-m|J'ai passé.
+enfant-m|J'ai visé le panier.
+papa|Bravo, Amir.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2187,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAS.001-06.xlsx
+++ b/stories/arbres/ATOM-JEU.BAS.001-06.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Blaise et papa sont au gymnase. Un petit &lt;emphasis level="moderate"&gt;panier&lt;/emphasis&gt; est accroché bas. Papa donne le ballon. Papa dit : on va passer le ballon. Ensuite, chacun a un lancer. Blaise passe. Papa rend. C'est le lancer de Blaise. Il lance vers le panier. Le ballon rentre. Papa a son lancer. Blaise dit : chacun un lancer. Ils se passent encore le ballon.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une gourde bleue roule toute seule. Elle fait un petit cercle. Le bois du gymnase est lisse. Ça sent le bois propre. Les chaussures d'Amir font toc. Toc. Toc. Tu entends l'écho, Amir ? Oui, papa. Ça répète. Une ligne jaune va tout droit. Elle brille un peu. Amir pose un doigt dessus. Elle est froide. C'est la ligne du gymnase. Le banc est vide. Un pull gris y dort. Papa pose le sac. La gourde s'arrête contre sa chaussure. Bravo. Tu l'as vue. En ce moment, Amir est au gymnase. Un petit panier est accroché bas. Le filet est blanc. Il bouge un peu. Le ballon orange est dans le sac. Papa le sort. Il rebondit une fois. Pon. On va passer le ballon. Ensuite, chacun a un lancer. Amir touche le ballon. Il est un peu grainé. Il est chaud, papa. Un peu, oui. Tu me le passes ? Amir passe le ballon. Papa le prend. Bravo. Tu as passé. Papa rend le ballon. C'est ton lancer, Amir. Amir regarde le panier. Il lance vers le panier. Le ballon touche le bord. Il rentre. Le filet fait chh. Il est dedans ! Bravo, Amir. Tu as visé le panier. Chacun a un lancer. Maintenant, c'est le mien. Papa lance. Le ballon rentre. Chacun un lancer. Oui. On se passe encore. Amir passe. Papa passe. Le bois fait un bruit doux. Amir attend. C'est encore son lancer. Il lance vers le panier. Le ballon rentre. Bravo. Tu as passé. Tu as visé. Chacun a eu un lancer.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Blaise joue au basket. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir joue au basket. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1588,7 +1588,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1618,7 +1617,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Blaise a passé le ballon. Il a visé le &lt;emphasis level="moderate"&gt;panier&lt;/emphasis&gt;. Chacun a eu un lancer.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a passé le ballon. Il a visé le panier. Chacun a eu un lancer. Tu as passé, Amir. Bravo. Tu as visé le panier. Chacun un lancer.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1766,7 +1765,6 @@
 enfant-m|Chacun un lancer.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,12 +1789,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range le ballon dans le sac. Amir essuie ses mains. Elles sont un peu chaudes. La gourde bleue est là. Tu bois une gorgée ? Oui, papa. L'eau est fraîche. On a visé le panier. Oui. On s'est passé le ballon. Chacun a eu un lancer. Bravo. Tu as fait du bon travail. Le pull gris est encore sur le banc. Amir le prend. Il sent le bois. Oui. Un peu. Merci. Leurs chaussures font toc dans le couloir. On rentre.</t>
+          <t>Papa range le ballon dans le sac. Amir essuie ses mains. Elles sont un peu chaudes. La gourde bleue est là. Tu bois une gorgée ? Oui, papa. L'eau est fraîche. On a visé le panier. Oui. On s'est passé le ballon. Chacun a eu un lancer. Bravo. Le pull gris est encore sur le banc. Amir le prend. Il sent le bois. Oui. Un peu. Merci. Leurs chaussures font toc dans le couloir. On rentre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa range le ballon. Blaise essuie ses &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa range le ballon dans le sac. Amir essuie ses mains. Elles sont un peu chaudes. La gourde bleue est là. Tu bois une gorgée ? Oui, papa. L'eau est fraîche. On a visé le panier. Oui. On s'est passé le ballon. Chacun a eu un lancer. Bravo. Le pull gris est encore sur le banc. Amir le prend. Il sent le bois. Oui. Un peu. Merci. Leurs chaussures font toc dans le couloir. On rentre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1943,7 +1941,6 @@
 enfant-m|On s'est passé le ballon.
 papa|Chacun a eu un lancer.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 narrateur|Le pull gris est encore sur le banc.
 narrateur|Amir le prend.
 enfant-m|Il sent le bois.
@@ -1983,12 +1980,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La gourde bleue rentre dans le sac. J'ai passé. J'ai visé le panier. Bravo, Amir. L'histoire est finie.</t>
+          <t>La gourde bleue rentre dans le sac. J'ai passé. J'ai visé le panier. Bravo, Amir.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La gourde bleue rentre dans le sac. J'ai passé. J'ai visé le panier. Bravo, Amir.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2126,11 +2123,9 @@
           <t>narrateur|La gourde bleue rentre dans le sac.
 enfant-m|J'ai passé.
 enfant-m|J'ai visé le panier.
-papa|Bravo, Amir.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Bravo, Amir.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2149,7 +2144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2194,6 +2189,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAS.001-06.xlsx
+++ b/stories/arbres/ATOM-JEU.BAS.001-06.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Blaise, papa</t>
+          <t>Amir, papa</t>
         </is>
       </c>
     </row>
